--- a/TAKO盃選手名單.xlsx
+++ b/TAKO盃選手名單.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638678A8-FF14-42E7-9CC4-D4313F7D8A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="87">
   <si>
     <t>隊伍名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -326,18 +327,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TOTAL是63人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鄺浿鏇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張琬璿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張嘉伶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智維亞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳信富</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李昱林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趙克立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盧珮文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范劭安</t>
+  </si>
+  <si>
+    <t>TOTAL是70人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -538,39 +570,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -850,721 +878,798 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="21.375" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C7" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C10" s="5">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C11" s="23">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B12" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C12" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B13" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C13" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B14" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C14" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B15" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C15" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C16" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B17" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C17" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C18" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B19" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C19" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="29" t="s">
+    <row r="20" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C20" s="5">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C21" s="24">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C30" s="5">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C31" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B32" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C32" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C42" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
+    <row r="43" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C43" s="5">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B44" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C44" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B45" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C45" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B46" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C46" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C47" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B48" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C48" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B49" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C49" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B50" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C50" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B51" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C51" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="17" t="s">
+    <row r="52" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B52" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C52" s="15">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B53" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C53" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B54" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C54" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B55" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C55" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B56" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C56" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B57" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C57" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B58" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C58" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B59" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C59" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B60" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C60" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="17" t="s">
+    <row r="61" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B61" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="19">
+      <c r="C61" s="15">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B62" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C62" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B63" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C63" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B64" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C64" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B65" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C65" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B66" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="20">
+      <c r="C66" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B67" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C67" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B68" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C68" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B69" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C69" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B70" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C70" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="4" t="s">
+    <row r="71" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B71" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C71" s="5">
         <v>1</v>
       </c>
     </row>
